--- a/spreadsheet-examples/spreadsheet-libraries/SAP Cloud ALM - Library Elements Template for Interface.xlsx
+++ b/spreadsheet-examples/spreadsheet-libraries/SAP Cloud ALM - Library Elements Template for Interface.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C02ED66-F5CB-4CBE-9C07-B90138F1007D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA38FA3-32FF-4275-A1F3-0F351D4FD0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library Elements" sheetId="1" r:id="rId1"/>
     <sheet name="Library Type" sheetId="3" r:id="rId2"/>
     <sheet name="Element Type" sheetId="6" r:id="rId3"/>
-    <sheet name="Categories" sheetId="4" r:id="rId4"/>
-    <sheet name="Help Portal" sheetId="5" r:id="rId5"/>
+    <sheet name="Help Portal" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Library Elements'!$A$1:$P$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Library Elements'!$A$1:$O$4</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -130,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
   <si>
     <t>Title</t>
   </si>
@@ -156,9 +155,6 @@
     <t>Middleware System Group</t>
   </si>
   <si>
-    <t>Category</t>
-  </si>
-  <si>
     <t>URL</t>
   </si>
   <si>
@@ -195,9 +191,6 @@
     <t>REST</t>
   </si>
   <si>
-    <t>Available Categories</t>
-  </si>
-  <si>
     <t>API</t>
   </si>
   <si>
@@ -213,21 +206,12 @@
     <t>HTTP / WebService</t>
   </si>
   <si>
-    <t>Other</t>
-  </si>
-  <si>
     <t>For detailed information on the creation of documents via spreadsheet, see SAP Help Portal.</t>
   </si>
   <si>
     <t>Odata</t>
   </si>
   <si>
-    <t>Odata V2</t>
-  </si>
-  <si>
-    <t>Odata V4</t>
-  </si>
-  <si>
     <t>General File-based Interface</t>
   </si>
   <si>
@@ -238,6 +222,24 @@
   </si>
   <si>
     <t>Element Type</t>
+  </si>
+  <si>
+    <t>Available Element Type</t>
+  </si>
+  <si>
+    <t>Other Not Listed Technology</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>MCP Server</t>
+  </si>
+  <si>
+    <t>BW Extractor</t>
+  </si>
+  <si>
+    <t>SLT Replication</t>
   </si>
 </sst>
 </file>
@@ -390,15 +392,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -724,77 +726,74 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:BR10"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.6"/>
+  <dimension ref="A1:BQ10"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="4.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.76171875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.234375" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.94921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5234375" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.76171875" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.94921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.85546875" style="3"/>
+    <col min="1" max="1" width="20.375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="4.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:69" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="D1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="10" t="s">
-        <v>14</v>
-      </c>
+      <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
@@ -832,118 +831,105 @@
       <c r="AY1" s="3"/>
       <c r="AZ1" s="3"/>
       <c r="BA1" s="3"/>
-      <c r="BB1" s="3"/>
-    </row>
-    <row r="2" spans="1:70" ht="15.6" x14ac:dyDescent="0.6">
+    </row>
+    <row r="2" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:70" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A3" s="5" t="s">
+      <c r="C3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:70" ht="15.6" x14ac:dyDescent="0.6">
+    </row>
+    <row r="4" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:70" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="AD7" s="7"/>
-      <c r="AE7" s="7"/>
-      <c r="AF7" s="7"/>
-      <c r="AG7" s="7"/>
-      <c r="AH7" s="7"/>
-      <c r="AI7" s="7"/>
-      <c r="AJ7" s="7"/>
-      <c r="AK7" s="7"/>
-      <c r="AL7" s="7"/>
-      <c r="AM7" s="7"/>
-      <c r="AN7" s="7"/>
-      <c r="AO7" s="7"/>
-      <c r="AP7" s="7"/>
-      <c r="AQ7" s="7"/>
-      <c r="AR7" s="7"/>
-      <c r="AS7" s="7"/>
-      <c r="AT7" s="7"/>
-      <c r="AU7" s="7"/>
-      <c r="AV7" s="7"/>
-      <c r="AW7" s="7"/>
-      <c r="AX7" s="7"/>
-      <c r="AY7" s="7"/>
-      <c r="AZ7" s="7"/>
-      <c r="BA7" s="7"/>
-      <c r="BB7" s="7"/>
-      <c r="BC7" s="7"/>
-      <c r="BD7" s="7"/>
-      <c r="BE7" s="7"/>
-      <c r="BF7" s="7"/>
-      <c r="BG7" s="7"/>
-      <c r="BH7" s="7"/>
-      <c r="BI7" s="7"/>
-      <c r="BJ7" s="7"/>
-      <c r="BK7" s="7"/>
-      <c r="BL7" s="7"/>
-      <c r="BM7" s="7"/>
-      <c r="BN7" s="7"/>
-      <c r="BO7" s="7"/>
-      <c r="BP7" s="7"/>
-      <c r="BQ7" s="7"/>
-      <c r="BR7" s="7"/>
-    </row>
-    <row r="10" spans="1:70" ht="15.6" x14ac:dyDescent="0.6"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="AC7" s="6"/>
+      <c r="AD7" s="6"/>
+      <c r="AE7" s="6"/>
+      <c r="AF7" s="6"/>
+      <c r="AG7" s="6"/>
+      <c r="AH7" s="6"/>
+      <c r="AI7" s="6"/>
+      <c r="AJ7" s="6"/>
+      <c r="AK7" s="6"/>
+      <c r="AL7" s="6"/>
+      <c r="AM7" s="6"/>
+      <c r="AN7" s="6"/>
+      <c r="AO7" s="6"/>
+      <c r="AP7" s="6"/>
+      <c r="AQ7" s="6"/>
+      <c r="AR7" s="6"/>
+      <c r="AS7" s="6"/>
+      <c r="AT7" s="6"/>
+      <c r="AU7" s="6"/>
+      <c r="AV7" s="6"/>
+      <c r="AW7" s="6"/>
+      <c r="AX7" s="6"/>
+      <c r="AY7" s="6"/>
+      <c r="AZ7" s="6"/>
+      <c r="BA7" s="6"/>
+      <c r="BB7" s="6"/>
+      <c r="BC7" s="6"/>
+      <c r="BD7" s="6"/>
+      <c r="BE7" s="6"/>
+      <c r="BF7" s="6"/>
+      <c r="BG7" s="6"/>
+      <c r="BH7" s="6"/>
+      <c r="BI7" s="6"/>
+      <c r="BJ7" s="6"/>
+      <c r="BK7" s="6"/>
+      <c r="BL7" s="6"/>
+      <c r="BM7" s="6"/>
+      <c r="BN7" s="6"/>
+      <c r="BO7" s="6"/>
+      <c r="BP7" s="6"/>
+      <c r="BQ7" s="6"/>
+    </row>
+    <row r="10" spans="1:69" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:P4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:O4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Choose Category" prompt=" " xr:uid="{349AE7D8-418A-43AD-AB5F-7535CB0800C0}">
-          <x14:formula1>
-            <xm:f>Categories!$A$2:$A$15</xm:f>
-          </x14:formula1>
-          <xm:sqref>J2:J10</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00923408-E181-4911-80FB-F3E14D738080}">
-          <x14:formula1>
-            <xm:f>'Element Type'!$A$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>D2:D20</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B06E6956-DE4B-4E62-B78B-6B3BB3772219}">
           <x14:formula1>
             <xm:f>'Library Type'!$A$2</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C20</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BBACDD30-8051-423B-828C-6F78B2856398}">
+          <x14:formula1>
+            <xm:f>'Element Type'!$A$2:$A$17</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D1048576</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -953,54 +939,54 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0148C08-9615-D040-B920-96C17CC67CC7}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="10.85546875" style="1"/>
+    <col min="3" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="3"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="3"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="3"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
     </row>
@@ -1012,20 +998,95 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8E81842-A3DA-4BFD-A81D-06817BFFC0A8}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:A17"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.6171875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A2" s="2" t="s">
-        <v>16</v>
+    <row r="17" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="10" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1034,119 +1095,27 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0303B768-7198-F346-AE46-E4635DF74FC2}">
-  <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
-  <cols>
-    <col min="1" max="1" width="25.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="11" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A1" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A2" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A3" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A4" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A5" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A6" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A7" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A8" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A9" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A10" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A11" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A12" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A13" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A14" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.6">
-      <c r="A15" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A15">
-    <sortCondition ref="A2:A15"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{574F8865-6568-43EE-85C4-2FD9BB5A44FB}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A4:H4"/>
-  <sheetFormatPr defaultColWidth="10.6171875" defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="10.6171875" style="4"/>
+    <col min="1" max="16384" width="10.625" style="4"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
